--- a/FPrak/Zeemann/Daten_Zeemann.xlsx
+++ b/FPrak/Zeemann/Daten_Zeemann.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10404"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/fynnlucca/Documents/Grundpraktikum-1/FPrak/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/391799d184623f23/Desktop/Universität/Grundpraktikum-1/FPrak/Zeemann/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AD1FC0CF-B972-EB4D-B5DE-15A96AE77AA5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="57" documentId="13_ncr:1_{AD1FC0CF-B972-EB4D-B5DE-15A96AE77AA5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CBB067F3-1EA7-4F3F-A555-0688ED6B2AD6}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="34560" windowHeight="21680" xr2:uid="{0DB0F654-E22D-D249-A523-4CBE440F9604}"/>
+    <workbookView xWindow="29130" yWindow="0" windowWidth="9360" windowHeight="20970" xr2:uid="{0DB0F654-E22D-D249-A523-4CBE440F9604}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5" uniqueCount="5">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
   <si>
     <t>Zeemann Effekt Versuch</t>
   </si>
@@ -51,6 +51,12 @@
   </si>
   <si>
     <t>B[mT]</t>
+  </si>
+  <si>
+    <t>Abweichung</t>
+  </si>
+  <si>
+    <t>Fit [mT]</t>
   </si>
 </sst>
 </file>
@@ -90,7 +96,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Standard" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -106,7 +112,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -422,118 +428,369 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DDE4EBC0-98E4-104E-BA8F-34E992D06032}">
-  <dimension ref="A3:B20"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <dimension ref="A3:K28"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.4"/>
   <sheetData>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A3" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A5" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A6" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A9" t="s">
         <v>3</v>
       </c>
       <c r="B9" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="C9" t="s">
+        <v>6</v>
+      </c>
+      <c r="D9" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A10">
         <v>0</v>
       </c>
       <c r="B10">
         <v>9</v>
       </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="C10">
+        <f>78.06*A10+17.49</f>
+        <v>17.489999999999998</v>
+      </c>
+      <c r="D10">
+        <f>ABS(B10-C10)/B10 * 100</f>
+        <v>94.333333333333314</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A11">
         <v>1</v>
       </c>
       <c r="B11">
         <v>88</v>
       </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="C11">
+        <f t="shared" ref="C11:C20" si="0">78.06*A11+17.49</f>
+        <v>95.55</v>
+      </c>
+      <c r="D11">
+        <f t="shared" ref="D11:D20" si="1">ABS(B11-C11)/B11 * 100</f>
+        <v>8.5795454545454515</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A12">
         <v>2</v>
       </c>
       <c r="B12">
         <v>163</v>
       </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="C12">
+        <f t="shared" si="0"/>
+        <v>173.61</v>
+      </c>
+      <c r="D12">
+        <f t="shared" si="1"/>
+        <v>6.5092024539877391</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A13">
         <v>3</v>
       </c>
       <c r="B13">
         <v>244</v>
       </c>
-    </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="C13">
+        <f t="shared" si="0"/>
+        <v>251.67000000000002</v>
+      </c>
+      <c r="D13">
+        <f t="shared" si="1"/>
+        <v>3.1434426229508263</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A14">
         <v>4</v>
       </c>
       <c r="B14">
         <v>334</v>
       </c>
-    </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="C14">
+        <f t="shared" si="0"/>
+        <v>329.73</v>
+      </c>
+      <c r="D14">
+        <f t="shared" si="1"/>
+        <v>1.2784431137724495</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A15">
         <v>5</v>
       </c>
       <c r="B15">
         <v>413</v>
       </c>
-    </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="C15">
+        <f t="shared" si="0"/>
+        <v>407.79</v>
+      </c>
+      <c r="D15">
+        <f t="shared" si="1"/>
+        <v>1.261501210653748</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A16">
         <v>6</v>
       </c>
       <c r="B16">
         <v>497</v>
       </c>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="C16">
+        <f t="shared" si="0"/>
+        <v>485.85</v>
+      </c>
+      <c r="D16">
+        <f t="shared" si="1"/>
+        <v>2.2434607645875206</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A17">
         <v>7</v>
       </c>
       <c r="B17">
         <v>579</v>
       </c>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="C17">
+        <f t="shared" si="0"/>
+        <v>563.91000000000008</v>
+      </c>
+      <c r="D17">
+        <f t="shared" si="1"/>
+        <v>2.6062176165802966</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A18">
         <v>8</v>
       </c>
       <c r="B18">
         <v>655</v>
       </c>
-    </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="C18">
+        <f t="shared" si="0"/>
+        <v>641.97</v>
+      </c>
+      <c r="D18">
+        <f t="shared" si="1"/>
+        <v>1.9893129770992324</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A19">
         <v>9</v>
       </c>
       <c r="B19">
         <v>715</v>
       </c>
-    </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="C19">
+        <f t="shared" si="0"/>
+        <v>720.03</v>
+      </c>
+      <c r="D19">
+        <f t="shared" si="1"/>
+        <v>0.70349650349649973</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A20">
         <v>10</v>
       </c>
       <c r="B20">
         <v>769</v>
+      </c>
+      <c r="C20">
+        <f t="shared" si="0"/>
+        <v>798.09</v>
+      </c>
+      <c r="D20">
+        <f t="shared" si="1"/>
+        <v>3.7828348504551403</v>
+      </c>
+    </row>
+    <row r="24" spans="1:11" x14ac:dyDescent="0.4">
+      <c r="C24">
+        <v>2</v>
+      </c>
+      <c r="D24">
+        <v>3</v>
+      </c>
+      <c r="E24">
+        <v>4</v>
+      </c>
+      <c r="F24">
+        <v>5</v>
+      </c>
+      <c r="G24">
+        <v>6</v>
+      </c>
+      <c r="H24">
+        <v>7</v>
+      </c>
+      <c r="I24">
+        <v>8</v>
+      </c>
+      <c r="J24">
+        <v>9</v>
+      </c>
+      <c r="K24">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="25" spans="1:11" x14ac:dyDescent="0.4">
+      <c r="B25">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="C25">
+        <v>122</v>
+      </c>
+      <c r="D25">
+        <v>121</v>
+      </c>
+      <c r="E25">
+        <v>117</v>
+      </c>
+      <c r="F25">
+        <v>114</v>
+      </c>
+      <c r="G25">
+        <v>111</v>
+      </c>
+      <c r="H25">
+        <v>107</v>
+      </c>
+      <c r="I25">
+        <v>105</v>
+      </c>
+      <c r="J25">
+        <v>102</v>
+      </c>
+      <c r="K25">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="26" spans="1:11" x14ac:dyDescent="0.4">
+      <c r="B26">
+        <v>3.1</v>
+      </c>
+      <c r="C26">
+        <v>136</v>
+      </c>
+      <c r="D26">
+        <v>138</v>
+      </c>
+      <c r="E26">
+        <v>140</v>
+      </c>
+      <c r="F26">
+        <v>143</v>
+      </c>
+      <c r="G26">
+        <v>146</v>
+      </c>
+      <c r="H26">
+        <v>150</v>
+      </c>
+      <c r="I26">
+        <v>152</v>
+      </c>
+      <c r="J26">
+        <v>154</v>
+      </c>
+      <c r="K26">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="27" spans="1:11" x14ac:dyDescent="0.4">
+      <c r="B27">
+        <v>1.2</v>
+      </c>
+      <c r="C27">
+        <v>224</v>
+      </c>
+      <c r="D27">
+        <v>222</v>
+      </c>
+      <c r="E27">
+        <v>220</v>
+      </c>
+      <c r="F27">
+        <v>218</v>
+      </c>
+      <c r="G27">
+        <v>216</v>
+      </c>
+      <c r="H27">
+        <v>214</v>
+      </c>
+      <c r="I27">
+        <v>213</v>
+      </c>
+      <c r="J27">
+        <v>211</v>
+      </c>
+      <c r="K27">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="28" spans="1:11" x14ac:dyDescent="0.4">
+      <c r="B28">
+        <v>3.2</v>
+      </c>
+      <c r="C28">
+        <v>229</v>
+      </c>
+      <c r="D28">
+        <v>231</v>
+      </c>
+      <c r="E28">
+        <v>233</v>
+      </c>
+      <c r="F28">
+        <v>235</v>
+      </c>
+      <c r="G28">
+        <v>238</v>
+      </c>
+      <c r="H28">
+        <v>239</v>
+      </c>
+      <c r="I28">
+        <v>241</v>
+      </c>
+      <c r="J28">
+        <v>241</v>
+      </c>
+      <c r="K28">
+        <v>243</v>
       </c>
     </row>
   </sheetData>
